--- a/assets/files/tabel_penjualan.xlsx
+++ b/assets/files/tabel_penjualan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\kursus\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7717DE9-937E-4402-8454-0B42CBC223A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45AD9B94-3234-4DC6-B446-60CC58B3D37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2AC92979-D444-434B-BBF4-28298A591A14}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="174" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -122,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -140,10 +140,11 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -458,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A856EC7-D778-43D7-8A64-013BA63C2490}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" customWidth="1"/>
@@ -625,31 +626,35 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="8">
+      <c r="B14" s="9">
         <f>SUM(B2:B13)</f>
         <v>180300000</v>
       </c>
       <c r="C14" s="8"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B16" s="8">
         <f>AVERAGE(B2:B13)</f>
         <v>15025000</v>
       </c>
-      <c r="C15" s="8"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="C16" s="8"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B17" s="8">
         <f>MAX(B2:B13)</f>
         <v>18500000</v>
       </c>
-      <c r="C16" s="8"/>
+      <c r="C17" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/assets/files/tabel_penjualan.xlsx
+++ b/assets/files/tabel_penjualan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\kursus\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45AD9B94-3234-4DC6-B446-60CC58B3D37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0572C864-203D-424A-B3D2-C94BF81D5D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2AC92979-D444-434B-BBF4-28298A591A14}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Bulan</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t>Komisi</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
@@ -102,12 +105,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -122,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -137,14 +146,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -476,7 +488,7 @@
       <c r="C1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="6">
+      <c r="E1" s="10">
         <v>0.05</v>
       </c>
     </row>
@@ -484,10 +496,10 @@
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="6">
         <v>12500000</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <f>B2*$E$1</f>
         <v>625000</v>
       </c>
@@ -496,10 +508,10 @@
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>11750000</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <f t="shared" ref="C3:C13" si="0">B3*$E$1</f>
         <v>587500</v>
       </c>
@@ -508,10 +520,10 @@
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>13200000</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="7">
         <f t="shared" si="0"/>
         <v>660000</v>
       </c>
@@ -520,10 +532,10 @@
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>14100000</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <f t="shared" si="0"/>
         <v>705000</v>
       </c>
@@ -532,10 +544,10 @@
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>15250000</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <f t="shared" si="0"/>
         <v>762500</v>
       </c>
@@ -544,10 +556,10 @@
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <v>13800000</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <f t="shared" si="0"/>
         <v>690000</v>
       </c>
@@ -556,10 +568,10 @@
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <v>16400000</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <f t="shared" si="0"/>
         <v>820000</v>
       </c>
@@ -568,10 +580,10 @@
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>15900000</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <f t="shared" si="0"/>
         <v>795000</v>
       </c>
@@ -580,10 +592,10 @@
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>14750000</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <f t="shared" si="0"/>
         <v>737500</v>
       </c>
@@ -592,10 +604,10 @@
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>17300000</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <f t="shared" si="0"/>
         <v>865000</v>
       </c>
@@ -605,10 +617,10 @@
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>16850000</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <f t="shared" si="0"/>
         <v>842500</v>
       </c>
@@ -617,24 +629,27 @@
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="6">
         <v>18500000</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <f t="shared" si="0"/>
         <v>925000</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="9">
+      <c r="A14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="8">
         <f>SUM(B2:B13)</f>
         <v>180300000</v>
       </c>
-      <c r="C14" s="8"/>
+      <c r="C14" s="7"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
@@ -644,7 +659,7 @@
         <f>AVERAGE(B2:B13)</f>
         <v>15025000</v>
       </c>
-      <c r="C16" s="8"/>
+      <c r="C16" s="7"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
@@ -654,7 +669,7 @@
         <f>MAX(B2:B13)</f>
         <v>18500000</v>
       </c>
-      <c r="C17" s="8"/>
+      <c r="C17" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
